--- a/vse-loti/339336224/spec-339336224.xlsx
+++ b/vse-loti/339336224/spec-339336224.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -497,19 +497,644 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х3.5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4.276</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4.276</v>
+      </c>
+      <c r="F2" t="n">
+        <v>49487.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>59385</v>
+      </c>
+      <c r="H2" t="n">
+        <v>211608.55</v>
+      </c>
+      <c r="I2" t="n">
+        <v>49487.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>59385</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ТРУБА 820Х10 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2.397</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2.397</v>
+      </c>
+      <c r="F3" t="n">
+        <v>64107.62</v>
+      </c>
+      <c r="G3" t="n">
+        <v>76929.14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>153665.97</v>
+      </c>
+      <c r="I3" t="n">
+        <v>64107.62</v>
+      </c>
+      <c r="J3" t="n">
+        <v>76929.14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ТРУБА 32Х3.2 СТ3СП ГОСТ3262</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51009.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>61211.04</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8518.540000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>51009.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>61211.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="F5" t="n">
+        <v>105482.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>126579.32</v>
+      </c>
+      <c r="H5" t="n">
+        <v>55800.39</v>
+      </c>
+      <c r="I5" t="n">
+        <v>105482.77</v>
+      </c>
+      <c r="J5" t="n">
+        <v>126579.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ТРУБА 133Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="F6" t="n">
+        <v>62724.47</v>
+      </c>
+      <c r="G6" t="n">
+        <v>75269.36</v>
+      </c>
+      <c r="H6" t="n">
+        <v>57518.34</v>
+      </c>
+      <c r="I6" t="n">
+        <v>62724.47</v>
+      </c>
+      <c r="J6" t="n">
+        <v>75269.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х4.5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>99150</v>
+      </c>
+      <c r="G7" t="n">
+        <v>118980</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23796</v>
+      </c>
+      <c r="I7" t="n">
+        <v>99150</v>
+      </c>
+      <c r="J7" t="n">
+        <v>118980</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х3.5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4.959</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4.959</v>
+      </c>
+      <c r="F8" t="n">
+        <v>70819.23</v>
+      </c>
+      <c r="G8" t="n">
+        <v>84983.08</v>
+      </c>
+      <c r="H8" t="n">
+        <v>351192.56</v>
+      </c>
+      <c r="I8" t="n">
+        <v>70819.23</v>
+      </c>
+      <c r="J8" t="n">
+        <v>84983.08</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х3.5 СТ3СП ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2.809</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2.809</v>
+      </c>
+      <c r="F9" t="n">
+        <v>89880</v>
+      </c>
+      <c r="G9" t="n">
+        <v>107856</v>
+      </c>
+      <c r="H9" t="n">
+        <v>252472.92</v>
+      </c>
+      <c r="I9" t="n">
+        <v>89880</v>
+      </c>
+      <c r="J9" t="n">
+        <v>107856</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ТРУБА 325Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4.503</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4.503</v>
+      </c>
+      <c r="F10" t="n">
+        <v>57066.66</v>
+      </c>
+      <c r="G10" t="n">
+        <v>68479.99000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>256971.17</v>
+      </c>
+      <c r="I10" t="n">
+        <v>57066.66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>68479.99000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ТРУБА 20Х2.8 СТ2ПС ГОСТ3262</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>76847.39999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>92216.88</v>
+      </c>
+      <c r="H11" t="n">
+        <v>307389.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>76847.39999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>92216.88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ТРУБА 630Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4.418</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4.418</v>
+      </c>
+      <c r="F12" t="n">
+        <v>117293.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>140752.08</v>
+      </c>
+      <c r="H12" t="n">
+        <v>518202.24</v>
+      </c>
+      <c r="I12" t="n">
+        <v>117293.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>140752.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ТРУБА 25Х3.2 СТ3СП ГОСТ3262</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F13" t="n">
+        <v>68758.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>82509.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1856.47</v>
+      </c>
+      <c r="I13" t="n">
+        <v>68758.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>82509.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ТРУБА 273Х8 СТ10 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="F14" t="n">
+        <v>79680.17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>95616.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>43106.97</v>
+      </c>
+      <c r="I14" t="n">
+        <v>79680.17</v>
+      </c>
+      <c r="J14" t="n">
+        <v>95616.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ТРУБА 219Х6 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.918</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4.918</v>
+      </c>
+      <c r="F15" t="n">
+        <v>63237</v>
+      </c>
+      <c r="G15" t="n">
+        <v>75884.39999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>310999.57</v>
+      </c>
+      <c r="I15" t="n">
+        <v>63237</v>
+      </c>
+      <c r="J15" t="n">
+        <v>75884.39999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х4.0 СТ20 ОЦИНК. ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="F16" t="n">
+        <v>85600</v>
+      </c>
+      <c r="G16" t="n">
+        <v>102720</v>
+      </c>
+      <c r="H16" t="n">
+        <v>14124</v>
+      </c>
+      <c r="I16" t="n">
+        <v>85600</v>
+      </c>
+      <c r="J16" t="n">
+        <v>102720</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ТРУБА 377Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="F17" t="n">
+        <v>55833.29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>66999.95</v>
+      </c>
+      <c r="H17" t="n">
+        <v>48798.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>55833.29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>66999.95</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ТРУБА 80Х4 СТ20 ГОСТ3262</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="F18" t="n">
+        <v>113922.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>136707.48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>33265.49</v>
+      </c>
+      <c r="I18" t="n">
+        <v>113922.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>136707.48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Источник: Обоснование НМЦ.docx.DOCX</t>
+      <c r="E19" s="2" t="n">
+        <v>36.032</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>2649287.08</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>2649287.08</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Источник: ВЛТС_ЭТЗ на децентрализованную поставку труб стальных для ВлТС в 2027 г_.xlsx</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339336224/spec-339336224.xlsx
+++ b/vse-loti/339336224/spec-339336224.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +441,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +512,7 @@
           <t>ТРУБА 76Х3.5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>4.276</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,22 +520,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>4.276</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>49487.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>59385</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>211608.55</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>49487.5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>59385</v>
       </c>
     </row>
@@ -541,7 +548,7 @@
           <t>ТРУБА 820Х10 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>2.397</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,22 +556,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>2.397</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>64107.62</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>76929.14</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>153665.97</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>64107.62</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>76929.14</v>
       </c>
     </row>
@@ -577,7 +584,7 @@
           <t>ТРУБА 32Х3.2 СТ3СП ГОСТ3262</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>0.167</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,22 +592,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="2" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>51009.2</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>61211.04</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>8518.540000000001</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>51009.2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>61211.04</v>
       </c>
     </row>
@@ -613,7 +620,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0.529</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -621,22 +628,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="2" t="n">
         <v>0.529</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>105482.77</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>126579.32</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>55800.39</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>105482.77</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3" t="n">
         <v>126579.32</v>
       </c>
     </row>
@@ -649,7 +656,7 @@
           <t>ТРУБА 133Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>0.917</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -657,22 +664,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="2" t="n">
         <v>0.917</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>62724.47</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>75269.36</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>57518.34</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>62724.47</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3" t="n">
         <v>75269.36</v>
       </c>
     </row>
@@ -685,7 +692,7 @@
           <t>ТРУБА 159Х4.5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>0.24</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -693,22 +700,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>0.24</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>99150</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>118980</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>23796</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>99150</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>118980</v>
       </c>
     </row>
@@ -721,7 +728,7 @@
           <t>ТРУБА 89Х3.5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>4.959</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -729,22 +736,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="2" t="n">
         <v>4.959</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>70819.23</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>84983.08</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>351192.56</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>70819.23</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3" t="n">
         <v>84983.08</v>
       </c>
     </row>
@@ -757,7 +764,7 @@
           <t>ТРУБА 57Х3.5 СТ3СП ГОСТ10705</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>2.809</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -765,22 +772,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="2" t="n">
         <v>2.809</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>89880</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>107856</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>252472.92</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>89880</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3" t="n">
         <v>107856</v>
       </c>
     </row>
@@ -793,7 +800,7 @@
           <t>ТРУБА 325Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>4.503</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -801,22 +808,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="2" t="n">
         <v>4.503</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>57066.66</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>68479.99000000001</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>256971.17</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>57066.66</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3" t="n">
         <v>68479.99000000001</v>
       </c>
     </row>
@@ -829,7 +836,7 @@
           <t>ТРУБА 20Х2.8 СТ2ПС ГОСТ3262</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -837,22 +844,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3" t="n">
         <v>76847.39999999999</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3" t="n">
         <v>92216.88</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3" t="n">
         <v>307389.6</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3" t="n">
         <v>76847.39999999999</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3" t="n">
         <v>92216.88</v>
       </c>
     </row>
@@ -865,7 +872,7 @@
           <t>ТРУБА 630Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>4.418</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -873,22 +880,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="2" t="n">
         <v>4.418</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3" t="n">
         <v>117293.4</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3" t="n">
         <v>140752.08</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3" t="n">
         <v>518202.24</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3" t="n">
         <v>117293.4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>140752.08</v>
       </c>
     </row>
@@ -901,7 +908,7 @@
           <t>ТРУБА 25Х3.2 СТ3СП ГОСТ3262</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>0.027</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -909,22 +916,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>0.027</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3" t="n">
         <v>68758.2</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3" t="n">
         <v>82509.84</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3" t="n">
         <v>1856.47</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3" t="n">
         <v>68758.2</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="3" t="n">
         <v>82509.84</v>
       </c>
     </row>
@@ -937,7 +944,7 @@
           <t>ТРУБА 273Х8 СТ10 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>0.541</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -945,22 +952,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>0.541</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3" t="n">
         <v>79680.17</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3" t="n">
         <v>95616.2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3" t="n">
         <v>43106.97</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="3" t="n">
         <v>79680.17</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="3" t="n">
         <v>95616.2</v>
       </c>
     </row>
@@ -973,7 +980,7 @@
           <t>ТРУБА 219Х6 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>4.918</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -981,22 +988,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="2" t="n">
         <v>4.918</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3" t="n">
         <v>63237</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3" t="n">
         <v>75884.39999999999</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3" t="n">
         <v>310999.57</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3" t="n">
         <v>63237</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3" t="n">
         <v>75884.39999999999</v>
       </c>
     </row>
@@ -1009,7 +1016,7 @@
           <t>ТРУБА 108Х4.0 СТ20 ОЦИНК. ГОСТ10705</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>0.165</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1017,22 +1024,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="2" t="n">
         <v>0.165</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3" t="n">
         <v>85600</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>102720</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>14124</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>85600</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="3" t="n">
         <v>102720</v>
       </c>
     </row>
@@ -1045,7 +1052,7 @@
           <t>ТРУБА 377Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>0.874</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1053,22 +1060,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>0.874</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3" t="n">
         <v>55833.29</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3" t="n">
         <v>66999.95</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3" t="n">
         <v>48798.3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3" t="n">
         <v>55833.29</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="3" t="n">
         <v>66999.95</v>
       </c>
     </row>
@@ -1081,7 +1088,7 @@
           <t>ТРУБА 80Х4 СТ20 ГОСТ3262</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>0.292</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1089,45 +1096,45 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="2" t="n">
         <v>0.292</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3" t="n">
         <v>113922.9</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3" t="n">
         <v>136707.48</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3" t="n">
         <v>33265.49</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3" t="n">
         <v>113922.9</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="3" t="n">
         <v>136707.48</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="5" t="n">
         <v>36.032</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="6" t="n">
         <v>2649287.08</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="6" t="n">
         <v>2649287.08</v>
       </c>
     </row>

--- a/vse-loti/339336224/spec-339336224.xlsx
+++ b/vse-loti/339336224/spec-339336224.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -61,16 +62,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +450,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +480,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,22 +511,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>4.276</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
+        <v>211608.56</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>49487.5</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>59385</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>211608.55</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>49487.5</v>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>59385</v>
       </c>
     </row>
@@ -556,22 +541,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>2.397</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
+        <v>153665.97</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>64107.62</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>76929.14</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>153665.97</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>64107.62</v>
-      </c>
-      <c r="J3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>76929.14</v>
       </c>
     </row>
@@ -592,22 +571,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.167</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
+        <v>8518.530000000001</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>51009.2</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>61211.04</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>8518.540000000001</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>51009.2</v>
-      </c>
-      <c r="J4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>61211.04</v>
       </c>
     </row>
@@ -628,22 +601,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>0.529</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
+        <v>55800.39</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>105482.77</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>126579.32</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>55800.39</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>105482.77</v>
-      </c>
-      <c r="J5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>126579.32</v>
       </c>
     </row>
@@ -664,22 +631,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.917</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
+        <v>57518.32</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>62724.47</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>75269.36</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>57518.34</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>62724.47</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>75269.36</v>
       </c>
     </row>
@@ -700,22 +661,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.24</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
+        <v>23796</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>99150</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>118980</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>23796</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>99150</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>118980</v>
       </c>
     </row>
@@ -736,22 +691,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>4.959</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
+        <v>351192.56</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>70819.23</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>84983.08</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>351192.56</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>70819.23</v>
-      </c>
-      <c r="J8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <v>84983.08</v>
       </c>
     </row>
@@ -772,22 +721,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>2.809</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
+        <v>252472.92</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>89880</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>107856</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>252472.92</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>89880</v>
-      </c>
-      <c r="J9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>107856</v>
       </c>
     </row>
@@ -808,22 +751,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>4.503</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
+        <v>256971.19</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>57066.66</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>68479.99000000001</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>256971.17</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>57066.66</v>
-      </c>
-      <c r="J10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>68479.99000000001</v>
       </c>
     </row>
@@ -836,7 +773,7 @@
           <t>ТРУБА 20Х2.8 СТ2ПС ГОСТ3262</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -844,22 +781,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="4" t="n">
+        <v>307389.6</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>76847.39999999999</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>92216.88</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>307389.6</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>76847.39999999999</v>
-      </c>
-      <c r="J11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>92216.88</v>
       </c>
     </row>
@@ -880,22 +811,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <v>4.418</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
+        <v>518202.25</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>117293.4</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>140752.08</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>518202.24</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>117293.4</v>
-      </c>
-      <c r="J12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>140752.08</v>
       </c>
     </row>
@@ -916,22 +841,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.027</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
+        <v>1856.47</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>68758.2</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>82509.84</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1856.47</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>68758.2</v>
-      </c>
-      <c r="J13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>82509.84</v>
       </c>
     </row>
@@ -952,22 +871,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.541</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
+        <v>43106.98</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>79680.17</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>95616.2</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>43106.97</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>79680.17</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>95616.2</v>
       </c>
     </row>
@@ -988,22 +901,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <v>4.918</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="4" t="n">
+        <v>310999.56</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>63237</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>75884.39999999999</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>310999.57</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>63237</v>
-      </c>
-      <c r="J15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <v>75884.39999999999</v>
       </c>
     </row>
@@ -1024,22 +931,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="3" t="n">
         <v>0.165</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="4" t="n">
+        <v>14124</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>85600</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>102720</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>14124</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>85600</v>
-      </c>
-      <c r="J16" s="3" t="n">
+      <c r="H16" s="4" t="n">
         <v>102720</v>
       </c>
     </row>
@@ -1060,22 +961,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.874</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="4" t="n">
+        <v>48798.3</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>55833.29</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>66999.95</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>48798.3</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>55833.29</v>
-      </c>
-      <c r="J17" s="3" t="n">
+      <c r="H17" s="4" t="n">
         <v>66999.95</v>
       </c>
     </row>
@@ -1096,50 +991,228 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.292</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
+        <v>33265.48</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>113922.9</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="H18" s="4" t="n">
         <v>136707.48</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>33265.49</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>113922.9</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>136707.48</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Таблица 2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Общие требования к условиям поставки</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Технические требования к продукции</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Гарантийный срок должен составлять не менее чем 24 месяца со дня получения Покупателем Продукции.</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Требование к размерам товара</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Подтверждение соответствия продукции предъявляемым требованиям</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Требования к порядку расчета</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Требования к Участнику закупки</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>36.032</v>
-      </c>
-      <c r="H19" s="6" t="n">
+      <c r="E27" s="7" t="n">
+        <v>83.032</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>2649287.08</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="F28" s="8" t="n">
         <v>2649287.08</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Источник: ВЛТС_ЭТЗ на децентрализованную поставку труб стальных для ВлТС в 2027 г_.xlsx</t>
         </is>
